--- a/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_9.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_9.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Panel_E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_E" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,8 +454,8 @@
     <col width="21" customWidth="1" min="20" max="20"/>
     <col width="38" customWidth="1" min="21" max="21"/>
     <col width="62" customWidth="1" min="22" max="22"/>
-    <col width="32" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="62" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="24" max="24"/>
     <col width="59" customWidth="1" min="25" max="25"/>
     <col width="43" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
@@ -1519,6 +1519,16 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="W21" s="1" t="inlineStr">
+        <is>
+          <t>p_value_scope</t>
+        </is>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>inference_scope</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1583,6 +1593,16 @@
           <t>usa_full_mechanistic_readiness_not_available_for_transmission_advantage_model</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1659,6 +1679,16 @@
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1733,6 +1763,16 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
         </is>
       </c>
     </row>
@@ -2354,8 +2394,8 @@
     <col width="21" customWidth="1" min="20" max="20"/>
     <col width="38" customWidth="1" min="21" max="21"/>
     <col width="62" customWidth="1" min="22" max="22"/>
-    <col width="32" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="62" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="24" max="24"/>
     <col width="59" customWidth="1" min="25" max="25"/>
     <col width="43" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
@@ -3419,6 +3459,16 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="W21" s="1" t="inlineStr">
+        <is>
+          <t>p_value_scope</t>
+        </is>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>inference_scope</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3483,6 +3533,16 @@
           <t>usa_full_mechanistic_readiness_not_available_for_transmission_advantage_model</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3559,6 +3619,16 @@
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3633,6 +3703,16 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
         </is>
       </c>
     </row>
@@ -4254,8 +4334,8 @@
     <col width="21" customWidth="1" min="20" max="20"/>
     <col width="38" customWidth="1" min="21" max="21"/>
     <col width="62" customWidth="1" min="22" max="22"/>
-    <col width="32" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="62" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="24" max="24"/>
     <col width="59" customWidth="1" min="25" max="25"/>
     <col width="43" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
@@ -5319,6 +5399,16 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="W21" s="1" t="inlineStr">
+        <is>
+          <t>p_value_scope</t>
+        </is>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>inference_scope</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5383,6 +5473,16 @@
           <t>usa_full_mechanistic_readiness_not_available_for_transmission_advantage_model</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5459,6 +5559,16 @@
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5533,6 +5643,16 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
         </is>
       </c>
     </row>
@@ -6154,8 +6274,8 @@
     <col width="21" customWidth="1" min="20" max="20"/>
     <col width="38" customWidth="1" min="21" max="21"/>
     <col width="62" customWidth="1" min="22" max="22"/>
-    <col width="32" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="62" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="24" max="24"/>
     <col width="59" customWidth="1" min="25" max="25"/>
     <col width="43" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
@@ -7219,6 +7339,16 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="W21" s="1" t="inlineStr">
+        <is>
+          <t>p_value_scope</t>
+        </is>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>inference_scope</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7283,6 +7413,16 @@
           <t>usa_full_mechanistic_readiness_not_available_for_transmission_advantage_model</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7359,6 +7499,16 @@
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7433,6 +7583,16 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
         </is>
       </c>
     </row>
@@ -8054,8 +8214,8 @@
     <col width="21" customWidth="1" min="20" max="20"/>
     <col width="38" customWidth="1" min="21" max="21"/>
     <col width="62" customWidth="1" min="22" max="22"/>
-    <col width="32" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="62" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="24" max="24"/>
     <col width="59" customWidth="1" min="25" max="25"/>
     <col width="43" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
@@ -9119,6 +9279,16 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="W21" s="1" t="inlineStr">
+        <is>
+          <t>p_value_scope</t>
+        </is>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>inference_scope</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9183,6 +9353,16 @@
           <t>usa_full_mechanistic_readiness_not_available_for_transmission_advantage_model</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9259,6 +9439,16 @@
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9335,6 +9525,16 @@
           <t>first_detection_year_anchor_with_balanced_12_month_pre_post_window</t>
         </is>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>within_diagnostic_model_wald_p_values_no_multiplicity_adjustment</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>archive_context_diagnostic_not_claim_generating</t>
+        </is>
+      </c>
     </row>
     <row r="25"/>
     <row r="26"/>
